--- a/model_info/det_gemini_realset.xlsx
+++ b/model_info/det_gemini_realset.xlsx
@@ -344,7 +344,7 @@
     <col width="4.4" min="12" max="12" bestFit="1" customWidth="1"/>
     <col width="5.5" min="13" max="13" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="14" max="14" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="15" max="15" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="15" max="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -393,7 +393,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="O1" s="0" t="n">
-        <v>0.5125</v>
+        <v>0.75625</v>
       </c>
     </row>
     <row r="2">
@@ -442,7 +442,7 @@
         <v>0.6154220815200304</v>
       </c>
       <c r="O2" s="0" t="n">
-        <v>0.4458333333333333</v>
+        <v>0.7053728070175438</v>
       </c>
     </row>
     <row r="3">
@@ -491,7 +491,7 @@
         <v>1.0</v>
       </c>
       <c r="O3" s="0" t="n">
-        <v>0.8</v>
+        <v>0.8761904761904762</v>
       </c>
     </row>
     <row r="4">
@@ -638,7 +638,7 @@
         <v>0.14005587822514343</v>
       </c>
       <c r="O6" s="0" t="n">
-        <v>0.038461538461538464</v>
+        <v>0.31089743589743585</v>
       </c>
     </row>
     <row r="7">
@@ -687,7 +687,7 @@
         <v>0.6428571428571429</v>
       </c>
       <c r="O7" s="0" t="n">
-        <v>0.13256448412698413</v>
+        <v>0.5085899343711844</v>
       </c>
     </row>
     <row r="8">
@@ -736,7 +736,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="O8" s="0" t="n">
-        <v>0.6166666666666667</v>
+        <v>0.7738505747126436</v>
       </c>
     </row>
     <row r="9">
@@ -883,7 +883,7 @@
         <v>0.75</v>
       </c>
       <c r="O11" s="0" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.8246527777777778</v>
       </c>
     </row>
     <row r="12">
@@ -932,7 +932,7 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="O12" s="0" t="n">
-        <v>0.13124999999999998</v>
+        <v>0.5248086734693878</v>
       </c>
     </row>
     <row r="13">
@@ -981,7 +981,7 @@
         <v>0.40033959725437446</v>
       </c>
       <c r="O13" s="0" t="n">
-        <v>0.2523809523809524</v>
+        <v>0.5949404761904762</v>
       </c>
     </row>
     <row r="14">
@@ -1030,7 +1030,7 @@
         <v>0.9285714285714286</v>
       </c>
       <c r="O14" s="0" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.8100649350649352</v>
       </c>
     </row>
     <row r="15">
@@ -1079,7 +1079,7 @@
         <v>0.8444144592599948</v>
       </c>
       <c r="O15" s="0" t="n">
-        <v>0.5816666666666668</v>
+        <v>0.7618478260869566</v>
       </c>
     </row>
     <row r="16">
@@ -1128,7 +1128,7 @@
         <v>0.9820136456817886</v>
       </c>
       <c r="O16" s="0" t="n">
-        <v>0.9555555555555557</v>
+        <v>0.9777777777777779</v>
       </c>
     </row>
     <row r="17">
@@ -1177,7 +1177,7 @@
         <v>0.5799820693848332</v>
       </c>
       <c r="O17" s="0" t="n">
-        <v>0.11607142857142858</v>
+        <v>0.48530844155844155</v>
       </c>
     </row>
     <row r="18">
@@ -1226,7 +1226,7 @@
         <v>0.6</v>
       </c>
       <c r="O18" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6447368421052632</v>
       </c>
     </row>
     <row r="19">
@@ -1275,7 +1275,7 @@
         <v>0.48369640170019296</v>
       </c>
       <c r="O19" s="0" t="n">
-        <v>0.3055555555555555</v>
+        <v>0.613562091503268</v>
       </c>
     </row>
   </sheetData>

--- a/model_info/det_gemini_realset.xlsx
+++ b/model_info/det_gemini_realset.xlsx
@@ -344,7 +344,7 @@
     <col width="4.4" min="12" max="12" bestFit="1" customWidth="1"/>
     <col width="5.5" min="13" max="13" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="14" max="14" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="15" max="15" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="15" max="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -393,7 +393,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="O1" s="0" t="n">
-        <v>0.75625</v>
+        <v>0.5125</v>
       </c>
     </row>
     <row r="2">
@@ -442,7 +442,7 @@
         <v>0.6154220815200304</v>
       </c>
       <c r="O2" s="0" t="n">
-        <v>0.7053728070175438</v>
+        <v>0.4301900584795321</v>
       </c>
     </row>
     <row r="3">
@@ -491,7 +491,7 @@
         <v>1.0</v>
       </c>
       <c r="O3" s="0" t="n">
-        <v>0.8761904761904762</v>
+        <v>0.7619047619047619</v>
       </c>
     </row>
     <row r="4">
@@ -638,7 +638,7 @@
         <v>0.14005587822514343</v>
       </c>
       <c r="O6" s="0" t="n">
-        <v>0.31089743589743585</v>
+        <v>0.022435897435897436</v>
       </c>
     </row>
     <row r="7">
@@ -687,7 +687,7 @@
         <v>0.6428571428571429</v>
       </c>
       <c r="O7" s="0" t="n">
-        <v>0.5085899343711844</v>
+        <v>0.11726858211233211</v>
       </c>
     </row>
     <row r="8">
@@ -736,7 +736,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="O8" s="0" t="n">
-        <v>0.7738505747126436</v>
+        <v>0.5741379310344827</v>
       </c>
     </row>
     <row r="9">
@@ -883,7 +883,7 @@
         <v>0.75</v>
       </c>
       <c r="O11" s="0" t="n">
-        <v>0.8246527777777778</v>
+        <v>0.6493055555555556</v>
       </c>
     </row>
     <row r="12">
@@ -932,7 +932,7 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="O12" s="0" t="n">
-        <v>0.5248086734693878</v>
+        <v>0.12053571428571427</v>
       </c>
     </row>
     <row r="13">
@@ -981,7 +981,7 @@
         <v>0.40033959725437446</v>
       </c>
       <c r="O13" s="0" t="n">
-        <v>0.5949404761904762</v>
+        <v>0.23660714285714285</v>
       </c>
     </row>
     <row r="14">
@@ -1030,7 +1030,7 @@
         <v>0.9285714285714286</v>
       </c>
       <c r="O14" s="0" t="n">
-        <v>0.8100649350649352</v>
+        <v>0.6282467532467533</v>
       </c>
     </row>
     <row r="15">
@@ -1079,7 +1079,7 @@
         <v>0.8444144592599948</v>
       </c>
       <c r="O15" s="0" t="n">
-        <v>0.7618478260869566</v>
+        <v>0.5479468599033818</v>
       </c>
     </row>
     <row r="16">
@@ -1128,7 +1128,7 @@
         <v>0.9820136456817886</v>
       </c>
       <c r="O16" s="0" t="n">
-        <v>0.9777777777777779</v>
+        <v>0.9555555555555557</v>
       </c>
     </row>
     <row r="17">
@@ -1177,7 +1177,7 @@
         <v>0.5799820693848332</v>
       </c>
       <c r="O17" s="0" t="n">
-        <v>0.48530844155844155</v>
+        <v>0.09918831168831169</v>
       </c>
     </row>
     <row r="18">
@@ -1226,7 +1226,7 @@
         <v>0.6</v>
       </c>
       <c r="O18" s="0" t="n">
-        <v>0.6447368421052632</v>
+        <v>0.39473684210526316</v>
       </c>
     </row>
     <row r="19">
@@ -1275,7 +1275,7 @@
         <v>0.48369640170019296</v>
       </c>
       <c r="O19" s="0" t="n">
-        <v>0.613562091503268</v>
+        <v>0.2815904139433551</v>
       </c>
     </row>
   </sheetData>
